--- a/output_data/charts/crashSeverityByType-Licking.xlsx
+++ b/output_data/charts/crashSeverityByType-Licking.xlsx
@@ -46,37 +46,37 @@
     <t>Left Turn</t>
   </si>
   <si>
+    <t>Parked Vehicle</t>
+  </si>
+  <si>
+    <t>Sideswipe - Passing</t>
+  </si>
+  <si>
     <t>Overturning</t>
   </si>
   <si>
-    <t>Parked Vehicle</t>
-  </si>
-  <si>
     <t>Animal</t>
   </si>
   <si>
-    <t>Sideswipe - Passing</t>
-  </si>
-  <si>
     <t>Right Turn</t>
   </si>
   <si>
+    <t>Other Object</t>
+  </si>
+  <si>
     <t>Pedalcycles</t>
   </si>
   <si>
+    <t>Other Non-Vehicle</t>
+  </si>
+  <si>
+    <t>Other Non-Collision</t>
+  </si>
+  <si>
+    <t>Sideswipe - Meeting</t>
+  </si>
+  <si>
     <t>Backing</t>
-  </si>
-  <si>
-    <t>Other Non-Collision</t>
-  </si>
-  <si>
-    <t>Other Object</t>
-  </si>
-  <si>
-    <t>Other Non-Vehicle</t>
-  </si>
-  <si>
-    <t>Sideswipe - Meeting</t>
   </si>
   <si>
     <t>Train</t>
@@ -237,37 +237,37 @@
                   <c:v>Left Turn</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>Parked Vehicle</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Sideswipe - Passing</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>Overturning</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>Parked Vehicle</c:v>
-                </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>Animal</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Sideswipe - Passing</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>Right Turn</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>Other Object</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>Pedalcycles</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
+                  <c:v>Other Non-Vehicle</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Other Non-Collision</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Sideswipe - Meeting</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>Backing</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Other Non-Collision</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>Other Object</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>Other Non-Vehicle</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>Sideswipe - Meeting</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>Train</c:v>
@@ -285,40 +285,40 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>40</c:v>
+                  <c:v>34.44444444444444</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13.68421052631579</c:v>
+                  <c:v>15.55555555555556</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>11.57894736842105</c:v>
+                  <c:v>8.888888888888889</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8.421052631578947</c:v>
+                  <c:v>8.888888888888889</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>7.368421052631578</c:v>
+                  <c:v>8.888888888888889</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.263157894736842</c:v>
+                  <c:v>6.666666666666667</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>4.210526315789473</c:v>
+                  <c:v>5.555555555555555</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.157894736842105</c:v>
+                  <c:v>3.333333333333333</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.105263157894737</c:v>
+                  <c:v>3.333333333333333</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>2.105263157894737</c:v>
+                  <c:v>2.222222222222222</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.052631578947368</c:v>
+                  <c:v>2.222222222222222</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.052631578947368</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
                   <c:v>0</c:v>
@@ -391,37 +391,37 @@
                   <c:v>Left Turn</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>Parked Vehicle</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Sideswipe - Passing</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>Overturning</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>Parked Vehicle</c:v>
-                </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>Animal</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Sideswipe - Passing</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>Right Turn</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>Other Object</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>Pedalcycles</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
+                  <c:v>Other Non-Vehicle</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Other Non-Collision</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Sideswipe - Meeting</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>Backing</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Other Non-Collision</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>Other Object</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>Other Non-Vehicle</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>Sideswipe - Meeting</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>Train</c:v>
@@ -439,61 +439,61 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>31.57894736842105</c:v>
+                  <c:v>32.43727598566309</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>16.95906432748538</c:v>
+                  <c:v>16.30824372759857</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>7.212475633528265</c:v>
+                  <c:v>7.347670250896058</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7.602339181286549</c:v>
+                  <c:v>7.347670250896058</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>5.458089668615984</c:v>
+                  <c:v>6.093189964157706</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.432748538011696</c:v>
+                  <c:v>6.272401433691756</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>5.263157894736842</c:v>
+                  <c:v>2.150537634408602</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1.754385964912281</c:v>
+                  <c:v>5.734767025089606</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2.339181286549707</c:v>
+                  <c:v>5.376344086021505</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>6.627680311890838</c:v>
+                  <c:v>1.792114695340502</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>1.949317738791423</c:v>
+                  <c:v>1.971326164874552</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>3.313840155945419</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>0.3898635477582846</c:v>
+                  <c:v>3.584229390681003</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.339181286549707</c:v>
+                  <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0</c:v>
+                  <c:v>2.508960573476703</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0</c:v>
+                  <c:v>0.1792114695340502</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.1949317738791423</c:v>
+                  <c:v>0.3584229390681004</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.5847953216374269</c:v>
+                  <c:v>0.5376344086021506</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -545,37 +545,37 @@
                   <c:v>Left Turn</c:v>
                 </c:pt>
                 <c:pt idx="6">
+                  <c:v>Parked Vehicle</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Sideswipe - Passing</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>Overturning</c:v>
                 </c:pt>
-                <c:pt idx="7">
-                  <c:v>Parked Vehicle</c:v>
-                </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>Animal</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Sideswipe - Passing</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>Right Turn</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>Other Object</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>Pedalcycles</c:v>
                 </c:pt>
-                <c:pt idx="12">
+                <c:pt idx="13">
+                  <c:v>Other Non-Vehicle</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Other Non-Collision</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Sideswipe - Meeting</c:v>
+                </c:pt>
+                <c:pt idx="16">
                   <c:v>Backing</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Other Non-Collision</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>Other Object</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>Other Non-Vehicle</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>Sideswipe - Meeting</c:v>
                 </c:pt>
                 <c:pt idx="17">
                   <c:v>Train</c:v>
@@ -593,61 +593,61 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="19"/>
                 <c:pt idx="0">
-                  <c:v>21.4380594859948</c:v>
+                  <c:v>21.09037900874635</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>13.40456251804794</c:v>
+                  <c:v>13.75510204081633</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1.801905861969391</c:v>
+                  <c:v>1.906705539358601</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>22.72596015015882</c:v>
+                  <c:v>22.14577259475218</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.7103667340456252</c:v>
+                  <c:v>0.80466472303207</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>5.792665319087496</c:v>
+                  <c:v>5.848396501457726</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.004909038406006</c:v>
+                  <c:v>4.011661807580174</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.915680046202715</c:v>
+                  <c:v>11.59183673469388</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>7.721628645682934</c:v>
+                  <c:v>0.956268221574344</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>11.36009240542882</c:v>
+                  <c:v>7.696793002915451</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.824140918278949</c:v>
+                  <c:v>3.043731778425656</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.415824429685244</c:v>
+                  <c:v>0.5772594752186588</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>3.829049956684955</c:v>
+                  <c:v>0.4256559766763849</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.836557897776494</c:v>
+                  <c:v>0.01166180758017493</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>0.5890846087207624</c:v>
+                  <c:v>1.871720116618076</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.01155067860236789</c:v>
+                  <c:v>0.05830903790087463</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.05775339301183945</c:v>
+                  <c:v>3.661807580174927</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>0.01732601790355184</c:v>
+                  <c:v>0.01166180758017493</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>0.5428818943112909</c:v>
+                  <c:v>0.5306122448979592</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1103,13 +1103,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>40</v>
+        <v>34.44444444444444</v>
       </c>
       <c r="C2" s="2">
-        <v>31.57894736842105</v>
+        <v>32.43727598566309</v>
       </c>
       <c r="D2" s="2">
-        <v>21.4380594859948</v>
+        <v>21.09037900874635</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1117,13 +1117,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2">
-        <v>13.68421052631579</v>
+        <v>15.55555555555556</v>
       </c>
       <c r="C3" s="2">
-        <v>16.95906432748538</v>
+        <v>16.30824372759857</v>
       </c>
       <c r="D3" s="2">
-        <v>13.40456251804794</v>
+        <v>13.75510204081633</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1131,13 +1131,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2">
-        <v>11.57894736842105</v>
+        <v>8.888888888888889</v>
       </c>
       <c r="C4" s="2">
-        <v>7.212475633528265</v>
+        <v>7.347670250896058</v>
       </c>
       <c r="D4" s="2">
-        <v>1.801905861969391</v>
+        <v>1.906705539358601</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1145,13 +1145,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2">
-        <v>8.421052631578947</v>
+        <v>8.888888888888889</v>
       </c>
       <c r="C5" s="2">
-        <v>7.602339181286549</v>
+        <v>7.347670250896058</v>
       </c>
       <c r="D5" s="2">
-        <v>22.72596015015882</v>
+        <v>22.14577259475218</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1159,13 +1159,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="2">
-        <v>7.368421052631578</v>
+        <v>8.888888888888889</v>
       </c>
       <c r="C6" s="2">
-        <v>5.458089668615984</v>
+        <v>6.093189964157706</v>
       </c>
       <c r="D6" s="2">
-        <v>0.7103667340456252</v>
+        <v>0.80466472303207</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1173,13 +1173,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="2">
-        <v>5.263157894736842</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="C7" s="2">
-        <v>6.432748538011696</v>
+        <v>6.272401433691756</v>
       </c>
       <c r="D7" s="2">
-        <v>5.792665319087496</v>
+        <v>5.848396501457726</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1187,13 +1187,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2">
-        <v>4.210526315789473</v>
+        <v>5.555555555555555</v>
       </c>
       <c r="C8" s="2">
-        <v>5.263157894736842</v>
+        <v>2.150537634408602</v>
       </c>
       <c r="D8" s="2">
-        <v>1.004909038406006</v>
+        <v>4.011661807580174</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1201,13 +1201,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="2">
-        <v>3.157894736842105</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="C9" s="2">
-        <v>1.754385964912281</v>
+        <v>5.734767025089606</v>
       </c>
       <c r="D9" s="2">
-        <v>3.915680046202715</v>
+        <v>11.59183673469388</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1215,13 +1215,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="2">
-        <v>2.105263157894737</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="C10" s="2">
-        <v>2.339181286549707</v>
+        <v>5.376344086021505</v>
       </c>
       <c r="D10" s="2">
-        <v>7.721628645682934</v>
+        <v>0.956268221574344</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1229,13 +1229,13 @@
         <v>13</v>
       </c>
       <c r="B11" s="2">
-        <v>2.105263157894737</v>
+        <v>2.222222222222222</v>
       </c>
       <c r="C11" s="2">
-        <v>6.627680311890838</v>
+        <v>1.792114695340502</v>
       </c>
       <c r="D11" s="2">
-        <v>11.36009240542882</v>
+        <v>7.696793002915451</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1243,13 +1243,13 @@
         <v>14</v>
       </c>
       <c r="B12" s="2">
-        <v>1.052631578947368</v>
+        <v>2.222222222222222</v>
       </c>
       <c r="C12" s="2">
-        <v>1.949317738791423</v>
+        <v>1.971326164874552</v>
       </c>
       <c r="D12" s="2">
-        <v>2.824140918278949</v>
+        <v>3.043731778425656</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1257,13 +1257,13 @@
         <v>15</v>
       </c>
       <c r="B13" s="2">
-        <v>1.052631578947368</v>
+        <v>0</v>
       </c>
       <c r="C13" s="2">
-        <v>3.313840155945419</v>
+        <v>0</v>
       </c>
       <c r="D13" s="2">
-        <v>0.415824429685244</v>
+        <v>0.5772594752186588</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1274,10 +1274,10 @@
         <v>0</v>
       </c>
       <c r="C14" s="2">
-        <v>0.3898635477582846</v>
+        <v>3.584229390681003</v>
       </c>
       <c r="D14" s="2">
-        <v>3.829049956684955</v>
+        <v>0.4256559766763849</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1288,10 +1288,10 @@
         <v>0</v>
       </c>
       <c r="C15" s="2">
-        <v>2.339181286549707</v>
+        <v>0</v>
       </c>
       <c r="D15" s="2">
-        <v>1.836557897776494</v>
+        <v>0.01166180758017493</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1302,10 +1302,10 @@
         <v>0</v>
       </c>
       <c r="C16" s="2">
-        <v>0</v>
+        <v>2.508960573476703</v>
       </c>
       <c r="D16" s="2">
-        <v>0.5890846087207624</v>
+        <v>1.871720116618076</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1316,10 +1316,10 @@
         <v>0</v>
       </c>
       <c r="C17" s="2">
-        <v>0</v>
+        <v>0.1792114695340502</v>
       </c>
       <c r="D17" s="2">
-        <v>0.01155067860236789</v>
+        <v>0.05830903790087463</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1330,10 +1330,10 @@
         <v>0</v>
       </c>
       <c r="C18" s="2">
-        <v>0.1949317738791423</v>
+        <v>0.3584229390681004</v>
       </c>
       <c r="D18" s="2">
-        <v>0.05775339301183945</v>
+        <v>3.661807580174927</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -1347,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="2">
-        <v>0.01732601790355184</v>
+        <v>0.01166180758017493</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -1358,10 +1358,10 @@
         <v>0</v>
       </c>
       <c r="C20" s="2">
-        <v>0.5847953216374269</v>
+        <v>0.5376344086021506</v>
       </c>
       <c r="D20" s="2">
-        <v>0.5428818943112909</v>
+        <v>0.5306122448979592</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/charts/crashSeverityByType-Licking.xlsx
+++ b/output_data/charts/crashSeverityByType-Licking.xlsx
@@ -89,8 +89,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode=""/>
+    <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -147,7 +148,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -179,7 +180,7 @@
               <a:rPr lang="en-US" sz="1400" baseline="0">
                 <a:latin typeface="Arial"/>
               </a:rPr>
-              <a:t>Crash Severity by Type of Crash - Licking County</a:t>
+              <a:t>Crash Severity by Type of Crash, Licking County, 2020-2024</a:t>
             </a:r>
           </a:p>
         </c:rich>
